--- a/03_ДЗ/ДЗ-1/ДЗ1_вар7_расчеты.xlsx
+++ b/03_ДЗ/ДЗ-1/ДЗ1_вар7_расчеты.xlsx
@@ -142,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -171,13 +171,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -819,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:J15"/>
+  <dimension ref="B1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1105,21 +1102,6 @@
       <c r="J14" s="3" t="inlineStr">
         <is>
           <t>δ = 5–10 мм</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Допустимая репрессия (скв. глубже 1200 м), МПа</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>ПБ п. 2.7.3.3: 2,5–3,0</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:U32"/>
+  <dimension ref="B1:U23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2031,307 +2013,6 @@
       <c r="J23" s="12" t="n"/>
       <c r="K23" s="12" t="n"/>
       <c r="L23" s="13" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Проверка репрессии и отсутствия поглощения (на подошве каждого подынтервала, принятая ρR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>z, м</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>ρR принятая</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Pпл(z), МПа</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Pгс(z), МПа</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Pпогл(z), МПа</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>ΔPрепр, МПа</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>репрессия, %</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>треб. ≥ %</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>ΔP ≤ доп.</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Pгс &lt; Pпогл</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>итог</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="8">
-        <f>C5</f>
-        <v/>
-      </c>
-      <c r="C27" s="11">
-        <f>E14</f>
-        <v/>
-      </c>
-      <c r="D27" s="14">
-        <f>G5*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B27/10^6</f>
-        <v/>
-      </c>
-      <c r="E27" s="14">
-        <f>C27*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B27/10^6</f>
-        <v/>
-      </c>
-      <c r="F27" s="14">
-        <f>H5*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B27/10^6</f>
-        <v/>
-      </c>
-      <c r="G27" s="14">
-        <f>E27-D27</f>
-        <v/>
-      </c>
-      <c r="H27" s="15">
-        <f>(E27/D27-1)*100</f>
-        <v/>
-      </c>
-      <c r="I27" s="15">
-        <f>(I5-1)*100</f>
-        <v/>
-      </c>
-      <c r="J27" s="8">
-        <f>IF(G27&lt;='1_Исходные данные'!$I$15,"да","нет")</f>
-        <v/>
-      </c>
-      <c r="K27" s="8">
-        <f>IF(E27&lt;F27,"да","нет")</f>
-        <v/>
-      </c>
-      <c r="L27" s="8">
-        <f>IF(AND(H27&gt;=I27-0.01,J27="да",K27="да"),"ОК","проверить")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="8">
-        <f>C6</f>
-        <v/>
-      </c>
-      <c r="C28" s="11">
-        <f>E15</f>
-        <v/>
-      </c>
-      <c r="D28" s="14">
-        <f>G6*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B28/10^6</f>
-        <v/>
-      </c>
-      <c r="E28" s="14">
-        <f>C28*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B28/10^6</f>
-        <v/>
-      </c>
-      <c r="F28" s="14">
-        <f>H6*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B28/10^6</f>
-        <v/>
-      </c>
-      <c r="G28" s="14">
-        <f>E28-D28</f>
-        <v/>
-      </c>
-      <c r="H28" s="15">
-        <f>(E28/D28-1)*100</f>
-        <v/>
-      </c>
-      <c r="I28" s="15">
-        <f>(I6-1)*100</f>
-        <v/>
-      </c>
-      <c r="J28" s="8">
-        <f>IF(G28&lt;='1_Исходные данные'!$I$15,"да","нет")</f>
-        <v/>
-      </c>
-      <c r="K28" s="8">
-        <f>IF(E28&lt;F28,"да","нет")</f>
-        <v/>
-      </c>
-      <c r="L28" s="8">
-        <f>IF(AND(H28&gt;=I28-0.01,J28="да",K28="да"),"ОК","проверить")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="8">
-        <f>C7</f>
-        <v/>
-      </c>
-      <c r="C29" s="11">
-        <f>E16</f>
-        <v/>
-      </c>
-      <c r="D29" s="14">
-        <f>G7*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B29/10^6</f>
-        <v/>
-      </c>
-      <c r="E29" s="14">
-        <f>C29*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B29/10^6</f>
-        <v/>
-      </c>
-      <c r="F29" s="14">
-        <f>H7*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B29/10^6</f>
-        <v/>
-      </c>
-      <c r="G29" s="14">
-        <f>E29-D29</f>
-        <v/>
-      </c>
-      <c r="H29" s="15">
-        <f>(E29/D29-1)*100</f>
-        <v/>
-      </c>
-      <c r="I29" s="15">
-        <f>(I7-1)*100</f>
-        <v/>
-      </c>
-      <c r="J29" s="8">
-        <f>IF(G29&lt;='1_Исходные данные'!$I$15,"да","нет")</f>
-        <v/>
-      </c>
-      <c r="K29" s="8">
-        <f>IF(E29&lt;F29,"да","нет")</f>
-        <v/>
-      </c>
-      <c r="L29" s="8">
-        <f>IF(AND(H29&gt;=I29-0.01,J29="да",K29="да"),"ОК","проверить")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="8">
-        <f>C8</f>
-        <v/>
-      </c>
-      <c r="C30" s="11">
-        <f>E16</f>
-        <v/>
-      </c>
-      <c r="D30" s="14">
-        <f>G8*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B30/10^6</f>
-        <v/>
-      </c>
-      <c r="E30" s="14">
-        <f>C30*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B30/10^6</f>
-        <v/>
-      </c>
-      <c r="F30" s="14">
-        <f>H8*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B30/10^6</f>
-        <v/>
-      </c>
-      <c r="G30" s="14">
-        <f>E30-D30</f>
-        <v/>
-      </c>
-      <c r="H30" s="15">
-        <f>(E30/D30-1)*100</f>
-        <v/>
-      </c>
-      <c r="I30" s="15">
-        <f>(I8-1)*100</f>
-        <v/>
-      </c>
-      <c r="J30" s="8">
-        <f>IF(G30&lt;='1_Исходные данные'!$I$15,"да","нет")</f>
-        <v/>
-      </c>
-      <c r="K30" s="8">
-        <f>IF(E30&lt;F30,"да","нет")</f>
-        <v/>
-      </c>
-      <c r="L30" s="8">
-        <f>IF(AND(H30&gt;=I30-0.01,J30="да",K30="да"),"ОК","проверить")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="8">
-        <f>C9</f>
-        <v/>
-      </c>
-      <c r="C31" s="11">
-        <f>E16</f>
-        <v/>
-      </c>
-      <c r="D31" s="14">
-        <f>G9*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B31/10^6</f>
-        <v/>
-      </c>
-      <c r="E31" s="14">
-        <f>C31*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B31/10^6</f>
-        <v/>
-      </c>
-      <c r="F31" s="14">
-        <f>H9*'1_Исходные данные'!$I$9*'1_Исходные данные'!$I$8*B31/10^6</f>
-        <v/>
-      </c>
-      <c r="G31" s="14">
-        <f>E31-D31</f>
-        <v/>
-      </c>
-      <c r="H31" s="15">
-        <f>(E31/D31-1)*100</f>
-        <v/>
-      </c>
-      <c r="I31" s="15">
-        <f>(I9-1)*100</f>
-        <v/>
-      </c>
-      <c r="J31" s="8">
-        <f>IF(G31&lt;='1_Исходные данные'!$I$15,"да","нет")</f>
-        <v/>
-      </c>
-      <c r="K31" s="8">
-        <f>IF(E31&lt;F31,"да","нет")</f>
-        <v/>
-      </c>
-      <c r="L31" s="8">
-        <f>IF(AND(H31&gt;=I31-0.01,J31="да",K31="да"),"ОК","проверить")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Репрессия в 1000–1200 м = 10 % (ровно норма), ниже 1200 м — больше 5 %; максимальное превышение над пластовым — у подошвы песчаника (1900 м) — не превышает 2,5 МПа.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2402,7 +2083,7 @@
       <c r="C5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="14">
         <f>'1_Исходные данные'!$I$7+10</f>
         <v/>
       </c>
@@ -2421,7 +2102,7 @@
       <c r="C6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="14">
         <f>'1_Исходные данные'!C6</f>
         <v/>
       </c>
@@ -2440,7 +2121,7 @@
       <c r="C7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="14">
         <f>'1_Исходные данные'!$I$5</f>
         <v/>
       </c>
@@ -2485,7 +2166,7 @@
           <t>Кондуктор</t>
         </is>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="14">
         <f>0</f>
         <v/>
       </c>
@@ -2505,7 +2186,7 @@
           <t>Промежуточная</t>
         </is>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="14">
         <f>MAX(0,D5-'1_Исходные данные'!$I$13)</f>
         <v/>
       </c>
@@ -2525,7 +2206,7 @@
           <t>Эксплуатационная</t>
         </is>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="14">
         <f>MAX(0,D6-'1_Исходные данные'!$I$13)</f>
         <v/>
       </c>
@@ -2687,15 +2368,15 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="16">
         <f>'1_Исходные данные'!$I$6</f>
         <v/>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="16">
         <f t="array" ref="E7">MIN(IF('ГОСТ 632-80 (ОТТМ)'!$E$4:$E$77&gt;=E6,'ГОСТ 632-80 (ОТТМ)'!$C$4:$C$77))</f>
         <v/>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="16">
         <f t="array" ref="F7">MIN(IF('ГОСТ 632-80 (ОТТМ)'!$E$4:$E$77&gt;=F6,'ГОСТ 632-80 (ОТТМ)'!$C$4:$C$77))</f>
         <v/>
       </c>
@@ -2740,10 +2421,10 @@
           <t>по расчёту на прочность</t>
         </is>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="17" t="n">
         <v>10.4</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="17" t="n">
         <v>8.9</v>
       </c>
     </row>
@@ -2855,15 +2536,15 @@
           <t>DB</t>
         </is>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="16">
         <f t="array" ref="D14">MIN(IF('ГОСТ 20692-2003 (долота)'!$B$4:$B$45&gt;=D13,'ГОСТ 20692-2003 (долота)'!$B$4:$B$45))</f>
         <v/>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="16">
         <f t="array" ref="E14">MIN(IF('ГОСТ 20692-2003 (долота)'!$B$4:$B$45&gt;=E13,'ГОСТ 20692-2003 (долота)'!$B$4:$B$45))</f>
         <v/>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="16">
         <f t="array" ref="F14">MIN(IF('ГОСТ 20692-2003 (долота)'!$B$4:$B$45&gt;=F13,'ГОСТ 20692-2003 (долота)'!$B$4:$B$45))</f>
         <v/>
       </c>
@@ -2943,7 +2624,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Примечания: 1) муфты — ОТТМ (трапецеидальная резьба, лучше герметичность для газовой скважины); 2) толщины стенок предварительные — окончательно по расчёту на прочность; для промежуточной допустимы s = 6,9…10,4 мм (d ≥ 156 мм), для кондуктора — любая из таблицы (d ≥ 232,3 мм); 3) ОК 244,5 мм для кондуктора не подходит: её наибольший d = 228,7 мм &lt; 232,3 мм.</t>
         </is>
@@ -3046,7 +2727,7 @@
           <t>4 1/2"</t>
         </is>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="19" t="n">
         <v>114.3</v>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -3054,7 +2735,7 @@
           <t>6"</t>
         </is>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="19" t="n">
         <v>152.4</v>
       </c>
       <c r="G5" s="15">
@@ -3085,7 +2766,7 @@
           <t>7"</t>
         </is>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="19" t="n">
         <v>177.8</v>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -3093,7 +2774,7 @@
           <t>8 1/2"</t>
         </is>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="19" t="n">
         <v>215.9</v>
       </c>
       <c r="G6" s="15">
@@ -3124,7 +2805,7 @@
           <t>9 5/8"</t>
         </is>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="19" t="n">
         <v>244.5</v>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -3132,7 +2813,7 @@
           <t>12 1/4"</t>
         </is>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="19" t="n">
         <v>311.2</v>
       </c>
       <c r="G7" s="15">
@@ -3256,14 +2937,14 @@
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Альтернатива по схеме: долото 8 3/4" (222,3 мм) под ОК 7" → ОК 10 3/4" (273,1 мм) → долото 14 1/2" (368,3 мм) станд. / 12 1/2" (317,5 мм) малый зазор.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Вывод: Ø эксплуатационной и промежуточной колонн совпадают (114,3 и 177,8 мм). Зарубежная методика допускает меньший зазор под 7" колонну (долото 215,9 вместо 222,3 мм), поэтому кондуктор получается 244,5 мм вместо 273,1 мм (долото 311,2 вместо 349,2 мм).</t>
         </is>
